--- a/01 - Projektmanagement und Tracking/Register - offene Annahmen.xlsx
+++ b/01 - Projektmanagement und Tracking/Register - offene Annahmen.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7b5b5fcebf85018c/Documents/personal Documents/01 - Studien/06 -MSc/1. Semester/SED605 - Requirements Engineering/Abgabe 1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stefan/Documents/GitHub/Study-Buddy-Gruppe06/01 - Projektmanagement und Tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{8B9FD99B-5A6D-4E41-B294-ADE2AF7AAB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2B4B804-007A-42F0-BB98-A78147B0E86B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBA90F7A-972F-C147-AED1-26E747BCEC4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" xr2:uid="{E83732BF-499C-4B74-BE66-E23E2CBB609D}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="68800" windowHeight="21120" xr2:uid="{E83732BF-499C-4B74-BE66-E23E2CBB609D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Fragen und Annahmen" sheetId="2" r:id="rId1"/>
+    <sheet name="Annahmen" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,14 +39,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>Typ</t>
-  </si>
-  <si>
     <t>Titel</t>
   </si>
   <si>
@@ -183,6 +180,22 @@
   </si>
   <si>
     <t>Always On</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Authentifizierungsmechanismus der FH </t>
+  </si>
+  <si>
+    <t>Alle</t>
+  </si>
+  <si>
+    <t>A-009</t>
+  </si>
+  <si>
+    <t>Die Integration des bestehenden Authentifizierungssystems hat keine Auswirkungen auf die Stakeholder, da alle bereits über Benutzerkonten verfügen müssen.
+Anders gesagt, wir nehmen an, dass kein Stakeholder ausgeschlossen wird.</t>
+  </si>
+  <si>
+    <t>Hoch</t>
   </si>
 </sst>
 </file>
@@ -277,10 +290,7 @@
     <cellStyle name="Heading 2" xfId="2" builtinId="17"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -331,20 +341,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A36AA336-C6B7-47A2-9B99-3DAB41517DC6}" name="Table1" displayName="Table1" ref="A4:K12" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
-  <autoFilter ref="A4:K12" xr:uid="{A36AA336-C6B7-47A2-9B99-3DAB41517DC6}"/>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{7E81B2A8-4CB9-48D8-BB1F-42539D6355A2}" name="ID" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{FBF9D28E-B5A2-4969-BE39-97DDC4F811DB}" name="Typ" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{D1E4BF83-A995-4F52-A9C6-3853EDD719EF}" name="Titel" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{56163B50-F8A9-457C-8C00-97828398652A}" name="Beschreibung / Details" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{0F87E05E-F98C-4F78-80C2-C09296A05494}" name="Kategorie" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{95DABB73-6E1D-4148-B1BD-71306776FB89}" name="Betroffene Stakeholder" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{76277E5E-640D-4EFE-B857-28F141AF0503}" name="Priorität (Bedeutung für das Projekt)" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{923EE2C7-97F3-4FDC-800A-85C1D65EAC14}" name="Komplexität (Aufwand zur Klärung)" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{68E90E79-F9C8-4D33-B6DD-2FE17298072F}" name="Status" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{92D8E496-6D14-4BC7-9AC5-620178C214DD}" name="Kommentar" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{11BBFB1D-D514-4EF1-B0E4-B3D54B449182}" name="Antwort / Entscheidung" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A36AA336-C6B7-47A2-9B99-3DAB41517DC6}" name="Table1" displayName="Table1" ref="A4:J13" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A4:J13" xr:uid="{A36AA336-C6B7-47A2-9B99-3DAB41517DC6}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{7E81B2A8-4CB9-48D8-BB1F-42539D6355A2}" name="ID" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{D1E4BF83-A995-4F52-A9C6-3853EDD719EF}" name="Titel" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{56163B50-F8A9-457C-8C00-97828398652A}" name="Beschreibung / Details" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{0F87E05E-F98C-4F78-80C2-C09296A05494}" name="Kategorie" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{95DABB73-6E1D-4148-B1BD-71306776FB89}" name="Betroffene Stakeholder" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{76277E5E-640D-4EFE-B857-28F141AF0503}" name="Priorität (Bedeutung für das Projekt)" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{923EE2C7-97F3-4FDC-800A-85C1D65EAC14}" name="Komplexität (Aufwand zur Klärung)" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{68E90E79-F9C8-4D33-B6DD-2FE17298072F}" name="Status" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{92D8E496-6D14-4BC7-9AC5-620178C214DD}" name="Kommentar" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{11BBFB1D-D514-4EF1-B0E4-B3D54B449182}" name="Antwort / Entscheidung" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -667,52 +676,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE1F0F60-56F3-40BB-9E9F-5F688C0C5A13}">
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="43.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="33.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="26.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="22.140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="43.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="33.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="31.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.1640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.1640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="29.83203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="22" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="3">
+      <c r="D1" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3">
         <v>0.1</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="D2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:10" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -743,19 +751,16 @@
       <c r="J4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>13</v>
@@ -763,172 +768,174 @@
       <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="112" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
